--- a/jadwal_smpn30_contoh.xlsx
+++ b/jadwal_smpn30_contoh.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guru" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,14 +11,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jadwal" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,18 +29,30 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0F6E56"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -61,15 +72,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -432,32 +446,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:D59"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>nama</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>nip</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>mapel</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>pin</t>
         </is>
@@ -466,220 +480,1044 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Siti Marlina, S.Pd.</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>198501012010012001</t>
-        </is>
-      </c>
+          <t>ABDUL RIFKI, S.Pd.I</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr"/>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Bahasa Indonesia</t>
+          <t>PAI</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1001</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Ahmad Fauzi, S.Pd.</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>198203152009011002</t>
-        </is>
-      </c>
+          <t>AFRIZAL, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Matematika</t>
+          <t>PJOK</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1002</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Dewi Anggraini, S.Pd.</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>199001202015022003</t>
-        </is>
-      </c>
+          <t>AKMAL MAULANA NASRULLAH, S.Pd</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>IPA</t>
+          <t>IPS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>1003</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Rudi Hartono, S.Pd.</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>197911082008011004</t>
-        </is>
-      </c>
+          <t>ALATAS FAHMI, S.Pd</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>IPS</t>
+          <t>PKN</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1004</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Nurul Hidayah, S.Pd.</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>198807252016022005</t>
-        </is>
-      </c>
+          <t>ASLAM AL HAQ, S.Sos</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Bahasa Inggris</t>
+          <t>PKN</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1005</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Bambang Sutrisno, S.Pd.</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>198012302007011006</t>
-        </is>
-      </c>
+          <t>DEDE FATURAHMAH, S.Pd</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>PPKn</t>
+          <t>IPA</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1106</t>
+          <t>1006</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Fitriani Rahman, S.Pd.</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>199203112018022007</t>
-        </is>
-      </c>
+          <t>DEWI SARTIKA, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Seni Budaya</t>
+          <t>Matematika</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1007</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Agus Setiawan, S.Pd.</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>197805192006011008</t>
-        </is>
-      </c>
+          <t>DYAH SETIYOWATI, S.Pd</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>PJOK</t>
+          <t>BK</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1008</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Yuli Astuti, S.Pd.</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>198609142014022009</t>
-        </is>
-      </c>
+          <t>EKA SHOLAHUDIN</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Prakarya</t>
+          <t>SBK</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1109</t>
+          <t>1009</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Hendra Gunawan, S.Kom.</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>199105082019011010</t>
-        </is>
-      </c>
+          <t>ELSITA LISNAWATI</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>IPA</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMA MAHBUBAH, S.Pd</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>IPA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1011</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ERHAMSYAH, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Bhs Indonesia</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1012</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>HAMIDAH, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Matematika</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1013</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>HANA CHARITA PRATIWI M, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SBK</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1014</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>IDA FARIDAH, S.Ag</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Bhs. Indonesia</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>JAMILAH, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>IPA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1016</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>JOKO PRAMUDIO, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>IPS</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1017</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>KOMARIAH, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Bahasa Inggris</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1018</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>LIA SAFITRI, S.Pd</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Bhs. Indonesia</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1019</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>LINDA WATI, S.Kom</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>Informatika</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1110</t>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>LU'LU' AZZAHRA, S.Pd</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BK</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1021</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>M. GURUH PRATAMA, S.Kom</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Infor &amp; Koding</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1022</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>MAILANI, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Bahasa Inggris</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MARIATUL QIBTIAH, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>IPA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MAULANA RIGANDI, S.Kom</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Infor, PJOK, Koding</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MEGAWATI KLARA MARBUN, S.Pd</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>IPS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MOCH. RUSDI, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Matematika</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1027</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>MUHAMAD NUR, S.T</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Matematika</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1028</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MUHAMMAD ANUGRAH, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SBK</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1029</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MUHAMMAD FIKRI, S.Pd</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PAI</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>MUHAMMAD WAHDAN NUH, S.Pd</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Bhs Indonesia</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1031</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NITA YULINDA, S.Pd</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Seni Budaya</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1032</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>NOVI RIZKY AMELIA, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>BK</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1033</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>NURAENI UTAMI, S.Or</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>PJOK</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1034</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>NURUL HIKMAH, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>IPS</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1035</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>NURUL KHOTIMAH</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>IPS</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1036</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PASCALIS HAMONANGAN, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>PJOK</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1037</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PRATAMA, M.Pd.</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>BK/PAI</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1038</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PUTRI IRMA SURYANI, S.Pd</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Bhs. Indonesia</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1039</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>RAHAYUNING DINI SEKAR ARUM, S.Pd</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SBK</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>RANI NOVIA RACHAYU, S.Pd</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Bhs Inggris</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1041</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>RINA KUSUMAYANTI, S.Pd</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>IPA</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1042</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ROMELAH, M.Pd.</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Matematika</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1043</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SHILFIYAH, S.Pd</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Bhs. Indonesia</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1044</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SILVIA NITA NUR ARYANTI, S.Pd</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Bhs. Indonesia</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1045</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SONDANG TITIAN PAULINA, S.Pd</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Matematika</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1046</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SUPARMAN, S.Pd.I</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>BK</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1047</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SYARIPAH, S.Pd</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Bhs. Indonesia</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1048</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>TAUFIQ AKBAR, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>PAI</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1049</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>TRI WAHYUNI, S.Pd</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>PKN</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1050</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>TUHFATUSTANIAH, S.Pd.I.</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>PAI</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1051</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>TUTY LATIFAH, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Bahasa Inggris</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1052</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ULVY WITRI HUMAIRAH, S.Pd</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>BK</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1053</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>UMI RIZKIAH, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>PKN &amp; Infor</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1054</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>UQON SYAJILY, S.H</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>PKN</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1055</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>WAHYU PRATAMA, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>PJOK</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1056</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>YATI FAZRIYAH, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Bahasa Inggris</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1057</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>YUSTINA MANURUNG, S.Kom</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>TIK</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1058</t>
         </is>
       </c>
     </row>
@@ -694,20 +1532,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>nama_kelas</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>kode_qr</t>
         </is>
@@ -716,60 +1554,360 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>VII-A</t>
+          <t>IX.1</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>KELAS-VIIA-SMPN30</t>
+          <t>KELAS-IX1-SMPN30</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>VII-B</t>
+          <t>IX.2</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>KELAS-VIIB-SMPN30</t>
+          <t>KELAS-IX2-SMPN30</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>VIII-A</t>
+          <t>IX.3</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>KELAS-VIIIA-SMPN30</t>
+          <t>KELAS-IX3-SMPN30</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>VIII-B</t>
+          <t>IX.4</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>KELAS-VIIIB-SMPN30</t>
+          <t>KELAS-IX4-SMPN30</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>IX-A</t>
+          <t>IX.5</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>KELAS-IXA-SMPN30</t>
+          <t>KELAS-IX5-SMPN30</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>IX.6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>KELAS-IX6-SMPN30</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>IX.7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>KELAS-IX7-SMPN30</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>IX.8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>KELAS-IX8-SMPN30</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>IX.9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>KELAS-IX9-SMPN30</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>IX.10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>KELAS-IX10-SMPN30</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>VII.1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>KELAS-VII1-SMPN30</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>VII.2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>KELAS-VII2-SMPN30</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>VII.3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>KELAS-VII3-SMPN30</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>VII.4</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>KELAS-VII4-SMPN30</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>VII.5</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>KELAS-VII5-SMPN30</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>VII.6</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>KELAS-VII6-SMPN30</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>VII.7</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>KELAS-VII7-SMPN30</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>VII.8</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>KELAS-VII8-SMPN30</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>VII.9</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>KELAS-VII9-SMPN30</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>VII.10</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>KELAS-VII10-SMPN30</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>VIII.1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>KELAS-VIII1-SMPN30</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>VIII.2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>KELAS-VIII2-SMPN30</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>VIII.3</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>KELAS-VIII3-SMPN30</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>VIII.4</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>KELAS-VIII4-SMPN30</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>VIII.5</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>KELAS-VIII5-SMPN30</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>VIII.6</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>KELAS-VIII6-SMPN30</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>VIII.7</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>KELAS-VIII7-SMPN30</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>VIII.8</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>KELAS-VIII8-SMPN30</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>VIII.9</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>KELAS-VIII9-SMPN30</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>VIII.10</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>KELAS-VIII10-SMPN30</t>
         </is>
       </c>
     </row>
@@ -784,50 +1922,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G193"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="4"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="6"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>guru_nama</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>kelas_nama</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>hari</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>jam_ke</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>jam_mulai</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>jam_selesai</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>mapel</t>
         </is>
@@ -836,567 +1974,567 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Siti Marlina, S.Pd.</t>
+          <t>PRATAMA, M.Pd.</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>VII-A</t>
+          <t>VII.1</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Senin</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Bahasa Indonesia</t>
+          <t>BK</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Ahmad Fauzi, S.Pd.</t>
+          <t>NURUL HIKMAH, S.Pd.</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>VII-A</t>
+          <t>VII.1</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Senin</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Matematika</t>
+          <t>IPS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Dewi Anggraini, S.Pd.</t>
+          <t>NURAENI UTAMI, S.Or</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>VII-A</t>
+          <t>VII.1</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Senin</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>IPA</t>
+          <t>PJOK</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Rudi Hartono, S.Pd.</t>
+          <t>UMI RIZKIAH, S.Pd.</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>VII-B</t>
+          <t>VII.1</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Senin</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>IPS</t>
+          <t>PKN &amp; Infor</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Nurul Hidayah, S.Pd.</t>
+          <t>NITA YULINDA, S.Pd</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>VII-B</t>
+          <t>VII.1</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Senin</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Bahasa Inggris</t>
+          <t>Seni Budaya</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Bambang Sutrisno, S.Pd.</t>
+          <t>DEWI SARTIKA, S.Pd.</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>VII-B</t>
+          <t>VII.1</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Senin</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>PPKn</t>
+          <t>Matematika</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Fitriani Rahman, S.Pd.</t>
+          <t>DEWI SARTIKA, S.Pd.</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>VIII-A</t>
+          <t>VII.2</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Senin</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Seni Budaya</t>
+          <t>Matematika</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Agus Setiawan, S.Pd.</t>
+          <t>NITA YULINDA, S.Pd</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>VIII-A</t>
+          <t>VII.2</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Senin</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>PJOK</t>
+          <t>Seni Budaya</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Yuli Astuti, S.Pd.</t>
+          <t>NURUL HIKMAH, S.Pd.</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>VIII-A</t>
+          <t>VII.2</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Senin</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Prakarya</t>
+          <t>IPS</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Hendra Gunawan, S.Kom.</t>
+          <t>M. GURUH PRATAMA, S.Kom</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>VIII-B</t>
+          <t>VII.2</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Senin</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Infor &amp; Koding</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Siti Marlina, S.Pd.</t>
+          <t>NITA YULINDA, S.Pd</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>VIII-B</t>
+          <t>VII.3</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Senin</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Bahasa Indonesia</t>
+          <t>Seni Budaya</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Ahmad Fauzi, S.Pd.</t>
+          <t>PRATAMA, M.Pd.</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>VIII-B</t>
+          <t>VII.3</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Senin</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Matematika</t>
+          <t>BK</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Dewi Anggraini, S.Pd.</t>
+          <t>DEWI SARTIKA, S.Pd.</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>IX-A</t>
+          <t>VII.3</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Senin</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>IPA</t>
+          <t>Matematika</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Rudi Hartono, S.Pd.</t>
+          <t>PRATAMA, M.Pd.</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>IX-A</t>
+          <t>VII.3</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Senin</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>IPS</t>
+          <t>BK</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Nurul Hidayah, S.Pd.</t>
+          <t>M. GURUH PRATAMA, S.Kom</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>IX-A</t>
+          <t>VII.3</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Senin</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Bahasa Inggris</t>
+          <t>Infor &amp; Koding</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Bambang Sutrisno, S.Pd.</t>
+          <t>UMI RIZKIAH, S.Pd.</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>VII-A</t>
+          <t>VII.3</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1406,34 +2544,34 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>PPKn</t>
+          <t>PKN &amp; Infor</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Fitriani Rahman, S.Pd.</t>
+          <t>NURAENI UTAMI, S.Or</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>VII-A</t>
+          <t>VII.4</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1443,34 +2581,34 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Seni Budaya</t>
+          <t>PJOK</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Agus Setiawan, S.Pd.</t>
+          <t>M. GURUH PRATAMA, S.Kom</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>VII-A</t>
+          <t>VII.4</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1480,34 +2618,34 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>PJOK</t>
+          <t>Infor &amp; Koding</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Yuli Astuti, S.Pd.</t>
+          <t>DEWI SARTIKA, S.Pd.</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>VII-B</t>
+          <t>VII.4</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1517,34 +2655,34 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Prakarya</t>
+          <t>Matematika</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Hendra Gunawan, S.Kom.</t>
+          <t>NITA YULINDA, S.Pd</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>VII-B</t>
+          <t>VII.4</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1554,34 +2692,34 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Seni Budaya</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Siti Marlina, S.Pd.</t>
+          <t>UMI RIZKIAH, S.Pd.</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>VII-B</t>
+          <t>VII.5</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1591,34 +2729,34 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Bahasa Indonesia</t>
+          <t>PKN &amp; Infor</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Ahmad Fauzi, S.Pd.</t>
+          <t>MAULANA RIGANDI, S.Kom</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>VIII-A</t>
+          <t>VII.5</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1628,34 +2766,34 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Matematika</t>
+          <t>Infor, PJOK, Koding</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Dewi Anggraini, S.Pd.</t>
+          <t>AKMAL MAULANA NASRULLAH, S.Pd</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>VIII-A</t>
+          <t>VII.5</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1665,34 +2803,34 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>IPA</t>
+          <t>IPS</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Rudi Hartono, S.Pd.</t>
+          <t>SUPARMAN, S.Pd.I</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>VIII-A</t>
+          <t>VII.5</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1702,34 +2840,34 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>IPS</t>
+          <t>BK dan PAI</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Nurul Hidayah, S.Pd.</t>
+          <t>AKMAL MAULANA NASRULLAH, S.Pd</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>VIII-B</t>
+          <t>VII.6</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1739,34 +2877,34 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Bahasa Inggris</t>
+          <t>IPS</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Bambang Sutrisno, S.Pd.</t>
+          <t>UMI RIZKIAH, S.Pd.</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>VIII-B</t>
+          <t>VII.6</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1776,34 +2914,34 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>PPKn</t>
+          <t>PKN &amp; Infor</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Fitriani Rahman, S.Pd.</t>
+          <t>NITA YULINDA, S.Pd</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>VIII-B</t>
+          <t>VII.6</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1813,17 +2951,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1835,12 +2973,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Agus Setiawan, S.Pd.</t>
+          <t>SUPARMAN, S.Pd.I</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>IX-A</t>
+          <t>VII.6</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1850,34 +2988,34 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>PJOK</t>
+          <t>BK dan PAI</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Yuli Astuti, S.Pd.</t>
+          <t>HAMIDAH, S.Pd.</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>IX-A</t>
+          <t>VII.6</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1887,34 +3025,34 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Prakarya</t>
+          <t>Matematika</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Hendra Gunawan, S.Kom.</t>
+          <t>M. GURUH PRATAMA, S.Kom</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>IX-A</t>
+          <t>VII.7</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1924,165 +3062,165 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Infor &amp; Koding</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Siti Marlina, S.Pd.</t>
+          <t>HAMIDAH, S.Pd.</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>VII-A</t>
+          <t>VII.7</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Rabu</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Bahasa Indonesia</t>
+          <t>Matematika</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Ahmad Fauzi, S.Pd.</t>
+          <t>SUPARMAN, S.Pd.I</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>VII-A</t>
+          <t>VII.7</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Rabu</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Matematika</t>
+          <t>BK dan PAI</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Dewi Anggraini, S.Pd.</t>
+          <t>TUTY LATIFAH, S.Pd.</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>VII-A</t>
+          <t>VII.7</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Rabu</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>IPA</t>
+          <t>Bahasa Inggris</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Rudi Hartono, S.Pd.</t>
+          <t>AKMAL MAULANA NASRULLAH, S.Pd</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>VII-B</t>
+          <t>VII.7</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Rabu</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -2094,735 +3232,735 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Nurul Hidayah, S.Pd.</t>
+          <t>UQON SYAJILY, S.H</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>VII-B</t>
+          <t>VII.8</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Rabu</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Bahasa Inggris</t>
+          <t>PKN</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Bambang Sutrisno, S.Pd.</t>
+          <t>TUTY LATIFAH, S.Pd.</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>VII-B</t>
+          <t>VII.8</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Rabu</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>PPKn</t>
+          <t>Bahasa Inggris</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Fitriani Rahman, S.Pd.</t>
+          <t>AKMAL MAULANA NASRULLAH, S.Pd</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>VIII-A</t>
+          <t>VII.8</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Rabu</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Seni Budaya</t>
+          <t>IPS</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Agus Setiawan, S.Pd.</t>
+          <t>HAMIDAH, S.Pd.</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>VIII-A</t>
+          <t>VII.8</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Rabu</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>PJOK</t>
+          <t>Matematika</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Yuli Astuti, S.Pd.</t>
+          <t>HAMIDAH, S.Pd.</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>VIII-A</t>
+          <t>VII.9</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Rabu</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Prakarya</t>
+          <t>Matematika</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Hendra Gunawan, S.Kom.</t>
+          <t>SUPARMAN, S.Pd.I</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>VIII-B</t>
+          <t>VII.9</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Rabu</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>BK dan PAI</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Siti Marlina, S.Pd.</t>
+          <t>TUTY LATIFAH, S.Pd.</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>VIII-B</t>
+          <t>VII.9</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Rabu</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Bahasa Indonesia</t>
+          <t>Bahasa Inggris</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Ahmad Fauzi, S.Pd.</t>
+          <t>LINDA WATI, S.Kom</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>VIII-B</t>
+          <t>VII.9</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Rabu</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Matematika</t>
+          <t>Informatika</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Dewi Anggraini, S.Pd.</t>
+          <t>TAUFIQ AKBAR, S.Pd.</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>IX-A</t>
+          <t>VII.9</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Rabu</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>IPA</t>
+          <t>PAI</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Rudi Hartono, S.Pd.</t>
+          <t>SUPARMAN, S.Pd.I</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>IX-A</t>
+          <t>VII.10</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Rabu</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>IPS</t>
+          <t>BK dan PAI</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Nurul Hidayah, S.Pd.</t>
+          <t>LINDA WATI, S.Kom</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>IX-A</t>
+          <t>VII.10</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Rabu</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Bahasa Inggris</t>
+          <t>Informatika</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Bambang Sutrisno, S.Pd.</t>
+          <t>HAMIDAH, S.Pd.</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>VII-A</t>
+          <t>VII.10</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Kamis</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>PPKn</t>
+          <t>Matematika</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Fitriani Rahman, S.Pd.</t>
+          <t>TAUFIQ AKBAR, S.Pd.</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>VII-A</t>
+          <t>VII.10</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Kamis</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Seni Budaya</t>
+          <t>PAI</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Agus Setiawan, S.Pd.</t>
+          <t>LINDA WATI, S.Kom</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>VII-A</t>
+          <t>VII.10</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Kamis</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>PJOK</t>
+          <t>Informatika</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Yuli Astuti, S.Pd.</t>
+          <t>TUTY LATIFAH, S.Pd.</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>VII-B</t>
+          <t>VII.10</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Kamis</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Prakarya</t>
+          <t>Bahasa Inggris</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Hendra Gunawan, S.Kom.</t>
+          <t>MUHAMMAD FIKRI, S.Pd</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>VII-B</t>
+          <t>VIII.1</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Kamis</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>PAI</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Siti Marlina, S.Pd.</t>
+          <t>LU'LU' AZZAHRA, S.Pd</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>VII-B</t>
+          <t>VIII.1</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Kamis</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Bahasa Indonesia</t>
+          <t>BK</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Ahmad Fauzi, S.Pd.</t>
+          <t>SILVIA NITA NUR ARYANTI, S.Pd</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>VIII-A</t>
+          <t>VIII.1</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Kamis</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Matematika</t>
+          <t>Bhs. Indonesia</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Dewi Anggraini, S.Pd.</t>
+          <t>YUSTINA MANURUNG, S.Kom</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>VIII-A</t>
+          <t>VIII.1</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Kamis</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>IPA</t>
+          <t>Informatika</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Rudi Hartono, S.Pd.</t>
+          <t>JOKO PRAMUDIO, S.Pd.</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>VIII-A</t>
+          <t>VIII.1</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Kamis</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -2834,698 +3972,698 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Nurul Hidayah, S.Pd.</t>
+          <t>YUSTINA MANURUNG, S.Kom</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>VIII-B</t>
+          <t>VIII.2</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Kamis</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Bahasa Inggris</t>
+          <t>Informatika</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Bambang Sutrisno, S.Pd.</t>
+          <t>JOKO PRAMUDIO, S.Pd.</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>VIII-B</t>
+          <t>VIII.2</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Kamis</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>PPKn</t>
+          <t>IPS</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Fitriani Rahman, S.Pd.</t>
+          <t>MARIATUL QIBTIAH, S.Pd.</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>VIII-B</t>
+          <t>VIII.2</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Kamis</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Seni Budaya</t>
+          <t>IPA</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Agus Setiawan, S.Pd.</t>
+          <t>HANA CHARITA PRATIWI M, S.Pd.</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>IX-A</t>
+          <t>VIII.2</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Kamis</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>PJOK</t>
+          <t>SBK</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Yuli Astuti, S.Pd.</t>
+          <t>MUHAMMAD FIKRI, S.Pd</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>IX-A</t>
+          <t>VIII.2</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Kamis</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Prakarya</t>
+          <t>PAI</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Hendra Gunawan, S.Kom.</t>
+          <t>LIA SAFITRI, S.Pd</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>IX-A</t>
+          <t>VIII.3</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Kamis</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Bhs. Indonesia</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Siti Marlina, S.Pd.</t>
+          <t>MUHAMMAD FIKRI, S.Pd</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>VII-A</t>
+          <t>VIII.3</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Jumat</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Bahasa Indonesia</t>
+          <t>PAI</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Ahmad Fauzi, S.Pd.</t>
+          <t>ALATAS FAHMI, S.Pd</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>VII-A</t>
+          <t>VIII.3</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Jumat</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Matematika</t>
+          <t>PKN</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Dewi Anggraini, S.Pd.</t>
+          <t>MUHAMAD NUR, S.T</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>VII-A</t>
+          <t>VIII.3</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Jumat</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>IPA</t>
+          <t>Matematika</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Rudi Hartono, S.Pd.</t>
+          <t>MARIATUL QIBTIAH, S.Pd.</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>VII-B</t>
+          <t>VIII.3</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Jumat</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>IPS</t>
+          <t>IPA</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Nurul Hidayah, S.Pd.</t>
+          <t>AFRIZAL, S.Pd.</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>VII-B</t>
+          <t>VIII.4</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Jumat</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Bahasa Inggris</t>
+          <t>PJOK</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Bambang Sutrisno, S.Pd.</t>
+          <t>MUHAMAD NUR, S.T</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>VII-B</t>
+          <t>VIII.4</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Jumat</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>PPKn</t>
+          <t>Matematika</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Fitriani Rahman, S.Pd.</t>
+          <t>JOKO PRAMUDIO, S.Pd.</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>VIII-A</t>
+          <t>VIII.4</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Jumat</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Seni Budaya</t>
+          <t>IPS</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Agus Setiawan, S.Pd.</t>
+          <t>YUSTINA MANURUNG, S.Kom</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>VIII-A</t>
+          <t>VIII.4</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Jumat</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>PJOK</t>
+          <t>Informatika</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Yuli Astuti, S.Pd.</t>
+          <t>ALATAS FAHMI, S.Pd</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>VIII-A</t>
+          <t>VIII.4</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Jumat</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Prakarya</t>
+          <t>PKN</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Hendra Gunawan, S.Kom.</t>
+          <t>JOKO PRAMUDIO, S.Pd.</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>VIII-B</t>
+          <t>VIII.5</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Jumat</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>IPS</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Siti Marlina, S.Pd.</t>
+          <t>EKA SHOLAHUDIN</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>VIII-B</t>
+          <t>VIII.5</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Jumat</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Bahasa Indonesia</t>
+          <t>SBK</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Ahmad Fauzi, S.Pd.</t>
+          <t>YUSTINA MANURUNG, S.Kom</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>VIII-B</t>
+          <t>VIII.5</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Jumat</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Matematika</t>
+          <t>Informatika</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Dewi Anggraini, S.Pd.</t>
+          <t>MARIATUL QIBTIAH, S.Pd.</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>IX-A</t>
+          <t>VIII.5</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Jumat</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -3537,74 +4675,4403 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Rudi Hartono, S.Pd.</t>
+          <t>MUHAMAD NUR, S.T</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>IX-A</t>
+          <t>VIII.5</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Jumat</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>IPS</t>
+          <t>Matematika</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Nurul Hidayah, S.Pd.</t>
+          <t>JAMILAH, S.Pd.</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>IX-A</t>
+          <t>VIII.6</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Jumat</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
+          <t>IPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>MOCH. RUSDI, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>VIII.6</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Matematika</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ULVY WITRI HUMAIRAH, S.Pd</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>VIII.6</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>BK</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>LIA SAFITRI, S.Pd</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>VIII.6</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Bhs. Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>EKA SHOLAHUDIN</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>VIII.6</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>SBK</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>PUTRI IRMA SURYANI, S.Pd</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>VIII.7</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Bhs. Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>YUSTINA MANURUNG, S.Kom</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>VIII.7</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Informatika</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>EKA SHOLAHUDIN</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>VIII.7</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>SBK</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>NURUL KHOTIMAH</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>VIII.7</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>IPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>MOCH. RUSDI, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>VIII.7</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Matematika</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>JAMILAH, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>VIII.7</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>IPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>NURUL KHOTIMAH</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>VIII.8</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>IPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>PUTRI IRMA SURYANI, S.Pd</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>VIII.8</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Bhs. Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>MUHAMMAD FIKRI, S.Pd</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>VIII.8</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>PAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>JAMILAH, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>VIII.8</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>IPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>MOCH. RUSDI, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>VIII.8</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Matematika</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>MOCH. RUSDI, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>VIII.9</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Matematika</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>ULVY WITRI HUMAIRAH, S.Pd</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>VIII.9</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>BK</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>JAMILAH, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>VIII.9</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>IPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>UQON SYAJILY, S.H</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>VIII.9</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>PKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>PUTRI IRMA SURYANI, S.Pd</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>VIII.9</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Bhs. Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>MAULANA RIGANDI, S.Kom</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>VIII.10</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Infor, PJOK, Koding</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>NURUL KHOTIMAH</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>VIII.10</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>IPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>PUTRI IRMA SURYANI, S.Pd</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>VIII.10</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Bhs. Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>ULVY WITRI HUMAIRAH, S.Pd</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>VIII.10</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>BK</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>UQON SYAJILY, S.H</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>VIII.10</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>PKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>ROMELAH, M.Pd.</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>IX.1</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Matematika</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>RANI NOVIA RACHAYU, S.Pd</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>IX.1</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Bhs Inggris</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>HANA CHARITA PRATIWI M, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>IX.1</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>SBK</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>ABDUL RIFKI, S.Pd.I</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>IX.1</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>PAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>ELSITA LISNAWATI</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>IX.1</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>IPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>SHILFIYAH, S.Pd</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>IX.1</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Bhs. Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>LINDA WATI, S.Kom</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>IX.2</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Informatika</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>SHILFIYAH, S.Pd</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>IX.2</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Bhs. Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>ABDUL RIFKI, S.Pd.I</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>IX.2</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>PAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>ROMELAH, M.Pd.</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>IX.2</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Matematika</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>HANA CHARITA PRATIWI M, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>IX.2</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>SBK</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>RANI NOVIA RACHAYU, S.Pd</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>IX.3</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Bhs Inggris</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>ROMELAH, M.Pd.</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>IX.3</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Matematika</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>SHILFIYAH, S.Pd</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>IX.3</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Bhs. Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>ALATAS FAHMI, S.Pd</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>IX.3</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>PKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>ABDUL RIFKI, S.Pd.I</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>IX.3</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>PAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>WAHYU PRATAMA, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>IX.4</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>PJOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>TRI WAHYUNI, S.Pd</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>IX.4</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>PKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>RANI NOVIA RACHAYU, S.Pd</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>IX.4</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Bhs Inggris</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>ELSITA LISNAWATI</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>IX.4</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>IPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>ELSITA LISNAWATI</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>IX.5</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>IPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>MEGAWATI KLARA MARBUN, S.Pd</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>IX.5</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>IPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>ROMELAH, M.Pd.</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>IX.5</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Matematika</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>SYARIPAH, S.Pd</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>IX.5</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Bhs. Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>YATI FAZRIYAH, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>IX.5</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
           <t>Bahasa Inggris</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>SYARIPAH, S.Pd</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>IX.6</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Bhs. Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>MUHAMMAD ANUGRAH, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>IX.6</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>SBK</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>EMA MAHBUBAH, S.Pd</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>IX.6</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>IPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>TRI WAHYUNI, S.Pd</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>IX.6</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>PKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>MEGAWATI KLARA MARBUN, S.Pd</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>IX.6</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>IPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>MUHAMMAD ANUGRAH, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>IX.7</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>SBK</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>YATI FAZRIYAH, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>IX.7</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Bahasa Inggris</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>WAHYU PRATAMA, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>IX.7</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>PJOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>ABDUL RIFKI, S.Pd.I</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>IX.7</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>PAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>SONDANG TITIAN PAULINA, S.Pd</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>IX.7</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Matematika</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>TRI WAHYUNI, S.Pd</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>IX.8</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>PKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>SONDANG TITIAN PAULINA, S.Pd</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>IX.8</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Matematika</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>MUHAMMAD ANUGRAH, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>IX.8</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>SBK</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>MEGAWATI KLARA MARBUN, S.Pd</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>IX.8</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>IPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>SYARIPAH, S.Pd</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>IX.8</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Bhs. Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>MEGAWATI KLARA MARBUN, S.Pd</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>IX.9</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>IPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>EMA MAHBUBAH, S.Pd</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>IX.9</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>IPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>MAULANA RIGANDI, S.Kom</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>IX.9</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Infor, PJOK, Koding</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>SONDANG TITIAN PAULINA, S.Pd</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>IX.9</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Matematika</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>MUHAMMAD ANUGRAH, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>IX.9</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>SBK</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>SONDANG TITIAN PAULINA, S.Pd</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>IX.10</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Matematika</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>TRI WAHYUNI, S.Pd</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>IX.10</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>PKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>YATI FAZRIYAH, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>IX.10</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Bahasa Inggris</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>MUHAMMAD ANUGRAH, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>IX.10</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>SBK</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>EMA MAHBUBAH, S.Pd</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>IX.10</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>IPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>SILVIA NITA NUR ARYANTI, S.Pd</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>IX.10</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Bhs. Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>NURUL HIKMAH, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>VII.1</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>IPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>PRATAMA, M.Pd.</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>VII.1</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>BK/PAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>KOMARIAH, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>VII.1</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Bahasa Inggris</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>NURUL HIKMAH, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>VII.2</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>IPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>PRATAMA, M.Pd.</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>VII.2</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>BK/PAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>KOMARIAH, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>VII.2</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Bahasa Inggris</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>PRATAMA, M.Pd.</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>VII.3</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>BK/PAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>NURUL HIKMAH, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>VII.4</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>IPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>KOMARIAH, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>VII.5</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Bahasa Inggris</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>KOMARIAH, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>VII.6</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Bahasa Inggris</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>MOCH. RUSDI, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>VII.6</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Matematika</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>TAUFIQ AKBAR, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>VII.9</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>PAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>TUTY LATIFAH, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>VII.10</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Bahasa Inggris</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>TAUFIQ AKBAR, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>VII.10</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>PAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>HANA CHARITA PRATIWI M, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>VIII.1</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>SBK</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>JOKO PRAMUDIO, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>VIII.2</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>IPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>AFRIZAL, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>VIII.3</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>PJOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>JOKO PRAMUDIO, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>VIII.4</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>IPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>JOKO PRAMUDIO, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>VIII.6</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>IPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>MOCH. RUSDI, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>VIII.7</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Matematika</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>MOCH. RUSDI, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>VIII.8</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Matematika</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>PASCALIS HAMONANGAN, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>VIII.9</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>PJOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>PASCALIS HAMONANGAN, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>VIII.10</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>PJOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>MOCH. RUSDI, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>VIII.10</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Matematika</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>DYAH SETIYOWATI, S.Pd</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>IX.1</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>BK</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>HANA CHARITA PRATIWI M, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>IX.1</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>SBK</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>ROMELAH, M.Pd.</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>IX.1</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Matematika</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>ROMELAH, M.Pd.</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>IX.2</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Matematika</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>DYAH SETIYOWATI, S.Pd</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>IX.2</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>BK</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>ABDUL RIFKI, S.Pd.I</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>IX.2</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>PAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>HANA CHARITA PRATIWI M, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>IX.2</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>SBK</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>HANA CHARITA PRATIWI M, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>IX.3</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>SBK</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>DYAH SETIYOWATI, S.Pd</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>IX.3</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>BK</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>ROMELAH, M.Pd.</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>IX.4</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Matematika</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>ABDUL RIFKI, S.Pd.I</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>IX.4</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>PAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>ABDUL RIFKI, S.Pd.I</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>IX.5</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>PAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>MUHAMMAD ANUGRAH, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>IX.5</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>SBK</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>ABDUL RIFKI, S.Pd.I</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>IX.6</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>PAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>ABDUL RIFKI, S.Pd.I</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>IX.8</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>PAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>MUHAMMAD ANUGRAH, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>IX.10</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>SBK</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>TAUFIQ AKBAR, S.Pd.</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>IX.10</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>PAI</t>
         </is>
       </c>
     </row>

--- a/jadwal_smpn30_contoh.xlsx
+++ b/jadwal_smpn30_contoh.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\alam\aplikasi kehadiran sekolah\presensi_guru\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9262196-B54B-4720-A64D-11884E7F7346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23B02D30-4950-4578-B04F-6C827061DE06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,9 +45,6 @@
     <t>mapel</t>
   </si>
   <si>
-    <t>PRATAMA, M.Pd.</t>
-  </si>
-  <si>
     <t>VII.1</t>
   </si>
   <si>
@@ -63,9 +60,6 @@
     <t>BK</t>
   </si>
   <si>
-    <t>NURUL HIKMAH, S.Pd.</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
@@ -75,9 +69,6 @@
     <t>IPS</t>
   </si>
   <si>
-    <t>NURAENI UTAMI, S.Or</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
@@ -90,9 +81,6 @@
     <t>PJOK</t>
   </si>
   <si>
-    <t>UMI RIZKIAH, S.Pd.</t>
-  </si>
-  <si>
     <t>6</t>
   </si>
   <si>
@@ -105,9 +93,6 @@
     <t>PKN &amp; Infor</t>
   </si>
   <si>
-    <t>NITA YULINDA, S.Pd</t>
-  </si>
-  <si>
     <t>7</t>
   </si>
   <si>
@@ -117,9 +102,6 @@
     <t>Seni Budaya</t>
   </si>
   <si>
-    <t>DEWI SARTIKA, S.Pd.</t>
-  </si>
-  <si>
     <t>8</t>
   </si>
   <si>
@@ -135,9 +117,6 @@
     <t>3</t>
   </si>
   <si>
-    <t>M. GURUH PRATAMA, S.Kom</t>
-  </si>
-  <si>
     <t>Infor &amp; Koding</t>
   </si>
   <si>
@@ -153,39 +132,21 @@
     <t>VII.5</t>
   </si>
   <si>
-    <t>MAULANA RIGANDI, S.Kom</t>
-  </si>
-  <si>
     <t>Infor, PJOK, Koding</t>
   </si>
   <si>
-    <t>AKMAL MAULANA NASRULLAH, S.Pd</t>
-  </si>
-  <si>
-    <t>SUPARMAN, S.Pd.I</t>
-  </si>
-  <si>
     <t>BK dan PAI</t>
   </si>
   <si>
     <t>VII.6</t>
   </si>
   <si>
-    <t>HAMIDAH, S.Pd.</t>
-  </si>
-  <si>
     <t>VII.7</t>
   </si>
   <si>
-    <t>TUTY LATIFAH, S.Pd.</t>
-  </si>
-  <si>
     <t>Bahasa Inggris</t>
   </si>
   <si>
-    <t>UQON SYAJILY, S.H</t>
-  </si>
-  <si>
     <t>VII.8</t>
   </si>
   <si>
@@ -195,72 +156,33 @@
     <t>VII.9</t>
   </si>
   <si>
-    <t>LINDA WATI, S.Kom</t>
-  </si>
-  <si>
     <t>Informatika</t>
   </si>
   <si>
-    <t>TAUFIQ AKBAR, S.Pd.</t>
-  </si>
-  <si>
     <t>PAI</t>
   </si>
   <si>
     <t>VII.10</t>
   </si>
   <si>
-    <t>MUHAMMAD FIKRI, S.Pd</t>
-  </si>
-  <si>
     <t>VIII.1</t>
   </si>
   <si>
-    <t>LU'LU' AZZAHRA, S.Pd</t>
-  </si>
-  <si>
-    <t>SILVIA NITA NUR ARYANTI, S.Pd</t>
-  </si>
-  <si>
     <t>Bhs. Indonesia</t>
   </si>
   <si>
-    <t>YUSTINA MANURUNG, S.Kom</t>
-  </si>
-  <si>
-    <t>JOKO PRAMUDIO, S.Pd.</t>
-  </si>
-  <si>
     <t>VIII.2</t>
   </si>
   <si>
-    <t>MARIATUL QIBTIAH, S.Pd.</t>
-  </si>
-  <si>
     <t>IPA</t>
   </si>
   <si>
-    <t>HANA CHARITA PRATIWI M, S.Pd.</t>
-  </si>
-  <si>
     <t>SBK</t>
   </si>
   <si>
-    <t>LIA SAFITRI, S.Pd</t>
-  </si>
-  <si>
     <t>VIII.3</t>
   </si>
   <si>
-    <t>ALATAS FAHMI, S.Pd</t>
-  </si>
-  <si>
-    <t>MUHAMAD NUR, S.T</t>
-  </si>
-  <si>
-    <t>AFRIZAL, S.Pd.</t>
-  </si>
-  <si>
     <t>VIII.4</t>
   </si>
   <si>
@@ -276,21 +198,9 @@
     <t>EKA SHOLAHUDIN</t>
   </si>
   <si>
-    <t>JAMILAH, S.Pd.</t>
-  </si>
-  <si>
     <t>VIII.6</t>
   </si>
   <si>
-    <t>MOCH. RUSDI, S.Pd.</t>
-  </si>
-  <si>
-    <t>ULVY WITRI HUMAIRAH, S.Pd</t>
-  </si>
-  <si>
-    <t>PUTRI IRMA SURYANI, S.Pd</t>
-  </si>
-  <si>
     <t>VIII.7</t>
   </si>
   <si>
@@ -306,69 +216,33 @@
     <t>VIII.10</t>
   </si>
   <si>
-    <t>ROMELAH, M.Pd.</t>
-  </si>
-  <si>
     <t>IX.1</t>
   </si>
   <si>
-    <t>RANI NOVIA RACHAYU, S.Pd</t>
-  </si>
-  <si>
     <t>Bhs Inggris</t>
   </si>
   <si>
-    <t>ABDUL RIFKI, S.Pd.I</t>
-  </si>
-  <si>
     <t>ELSITA LISNAWATI</t>
   </si>
   <si>
-    <t>SHILFIYAH, S.Pd</t>
-  </si>
-  <si>
     <t>IX.2</t>
   </si>
   <si>
     <t>IX.3</t>
   </si>
   <si>
-    <t>WAHYU PRATAMA, S.Pd.</t>
-  </si>
-  <si>
     <t>IX.4</t>
   </si>
   <si>
-    <t>TRI WAHYUNI, S.Pd</t>
-  </si>
-  <si>
     <t>IX.5</t>
   </si>
   <si>
-    <t>MEGAWATI KLARA MARBUN, S.Pd</t>
-  </si>
-  <si>
-    <t>SYARIPAH, S.Pd</t>
-  </si>
-  <si>
-    <t>YATI FAZRIYAH, S.Pd.</t>
-  </si>
-  <si>
     <t>IX.6</t>
   </si>
   <si>
-    <t>MUHAMMAD ANUGRAH, S.Pd.</t>
-  </si>
-  <si>
-    <t>EMA MAHBUBAH, S.Pd</t>
-  </si>
-  <si>
     <t>IX.7</t>
   </si>
   <si>
-    <t>SONDANG TITIAN PAULINA, S.Pd</t>
-  </si>
-  <si>
     <t>IX.8</t>
   </si>
   <si>
@@ -381,15 +255,6 @@
     <t>BK/PAI</t>
   </si>
   <si>
-    <t>KOMARIAH, S.Pd.</t>
-  </si>
-  <si>
-    <t>PASCALIS HAMONANGAN, S.Pd.</t>
-  </si>
-  <si>
-    <t>DYAH SETIYOWATI, S.Pd</t>
-  </si>
-  <si>
     <t>nama</t>
   </si>
   <si>
@@ -417,9 +282,6 @@
     <t>1005</t>
   </si>
   <si>
-    <t>DEDE FATURAHMAH, S.Pd</t>
-  </si>
-  <si>
     <t>1006</t>
   </si>
   <si>
@@ -438,9 +300,6 @@
     <t>1011</t>
   </si>
   <si>
-    <t>ERHAMSYAH, S.Pd.</t>
-  </si>
-  <si>
     <t>Bhs Indonesia</t>
   </si>
   <si>
@@ -453,9 +312,6 @@
     <t>1014</t>
   </si>
   <si>
-    <t>IDA FARIDAH, S.Ag</t>
-  </si>
-  <si>
     <t>1015</t>
   </si>
   <si>
@@ -480,9 +336,6 @@
     <t>1022</t>
   </si>
   <si>
-    <t>MAILANI, S.Pd.</t>
-  </si>
-  <si>
     <t>1023</t>
   </si>
   <si>
@@ -507,18 +360,12 @@
     <t>1030</t>
   </si>
   <si>
-    <t>MUHAMMAD WAHDAN NUH, S.Pd</t>
-  </si>
-  <si>
     <t>1031</t>
   </si>
   <si>
     <t>1032</t>
   </si>
   <si>
-    <t>NOVI RIZKY AMELIA, S.Pd.</t>
-  </si>
-  <si>
     <t>1033</t>
   </si>
   <si>
@@ -540,18 +387,12 @@
     <t>1039</t>
   </si>
   <si>
-    <t>RAHAYUNING DINI SEKAR ARUM, S.Pd</t>
-  </si>
-  <si>
     <t>1040</t>
   </si>
   <si>
     <t>1041</t>
   </si>
   <si>
-    <t>RINA KUSUMAYANTI, S.Pd</t>
-  </si>
-  <si>
     <t>1042</t>
   </si>
   <si>
@@ -579,9 +420,6 @@
     <t>1050</t>
   </si>
   <si>
-    <t>TUHFATUSTANIAH, S.Pd.I.</t>
-  </si>
-  <si>
     <t>1051</t>
   </si>
   <si>
@@ -709,13 +547,175 @@
   </si>
   <si>
     <t>Kamis</t>
+  </si>
+  <si>
+    <t>IDA FARIDAH</t>
+  </si>
+  <si>
+    <t>ABDUL RIFKII</t>
+  </si>
+  <si>
+    <t>AFRIZAL</t>
+  </si>
+  <si>
+    <t>DEWI SARTIKA</t>
+  </si>
+  <si>
+    <t>ERHAMSYAH</t>
+  </si>
+  <si>
+    <t>HAMIDAH</t>
+  </si>
+  <si>
+    <t>HANA CHARITA PRATIWI M</t>
+  </si>
+  <si>
+    <t>JAMILAH</t>
+  </si>
+  <si>
+    <t>JOKO PRAMUDIO</t>
+  </si>
+  <si>
+    <t>KOMARIAH</t>
+  </si>
+  <si>
+    <t>MAILANI</t>
+  </si>
+  <si>
+    <t>MARIATUL QIBTIAH</t>
+  </si>
+  <si>
+    <t>MOCH. RUSDI</t>
+  </si>
+  <si>
+    <t>MUHAMMAD ANUGRAH</t>
+  </si>
+  <si>
+    <t>NOVI RIZKY AMELIA</t>
+  </si>
+  <si>
+    <t>NURUL HIKMAH</t>
+  </si>
+  <si>
+    <t>PASCALIS HAMONANGAN</t>
+  </si>
+  <si>
+    <t>SUPARMANI</t>
+  </si>
+  <si>
+    <t>TAUFIQ AKBAR</t>
+  </si>
+  <si>
+    <t>TUTY LATIFAH</t>
+  </si>
+  <si>
+    <t>UMI RIZKIAH</t>
+  </si>
+  <si>
+    <t>WAHYU PRATAMA</t>
+  </si>
+  <si>
+    <t>YATI FAZRIYAH</t>
+  </si>
+  <si>
+    <t>AKMAL MAULANA NASRULLAH</t>
+  </si>
+  <si>
+    <t>ALATAS FAHMI</t>
+  </si>
+  <si>
+    <t>DEDE FATURAHMAH</t>
+  </si>
+  <si>
+    <t>DYAH SETIYOWATI</t>
+  </si>
+  <si>
+    <t>EMA MAHBUBAH</t>
+  </si>
+  <si>
+    <t>LIA SAFITRI</t>
+  </si>
+  <si>
+    <t>LU'LU' AZZAHRA</t>
+  </si>
+  <si>
+    <t>MEGAWATI KLARA MARBUN</t>
+  </si>
+  <si>
+    <t>MUHAMMAD FIKRI</t>
+  </si>
+  <si>
+    <t>MUHAMMAD WAHDAN NUH</t>
+  </si>
+  <si>
+    <t>NITA YULINDA</t>
+  </si>
+  <si>
+    <t>PUTRI IRMA SURYANI</t>
+  </si>
+  <si>
+    <t>RAHAYUNING DINI SEKAR ARUM</t>
+  </si>
+  <si>
+    <t>RANI NOVIA RACHAYU</t>
+  </si>
+  <si>
+    <t>RINA KUSUMAYANTI</t>
+  </si>
+  <si>
+    <t>SHILFIYAH</t>
+  </si>
+  <si>
+    <t>SILVIA NITA NUR ARYANTI</t>
+  </si>
+  <si>
+    <t>SONDANG TITIAN PAULINA</t>
+  </si>
+  <si>
+    <t>SYARIPAH</t>
+  </si>
+  <si>
+    <t>TRI WAHYUNI</t>
+  </si>
+  <si>
+    <t>ULVY WITRI HUMAIRAH</t>
+  </si>
+  <si>
+    <t>LINDA WATI</t>
+  </si>
+  <si>
+    <t>M. GURUH PRATAMA</t>
+  </si>
+  <si>
+    <t>MAULANA RIGANDI</t>
+  </si>
+  <si>
+    <t>YUSTINA MANURUNG</t>
+  </si>
+  <si>
+    <t>MUHAMAD NUR</t>
+  </si>
+  <si>
+    <t>NURAENI UTAMI</t>
+  </si>
+  <si>
+    <t>PRATAMA</t>
+  </si>
+  <si>
+    <t>ROMELAH</t>
+  </si>
+  <si>
+    <t>TUHFATUSTANIAHI</t>
+  </si>
+  <si>
+    <t>UQON SYAJILY</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -732,6 +732,28 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -759,12 +781,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1078,667 +1103,716 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>122</v>
+        <v>77</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>123</v>
+        <v>78</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A31" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A32" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A35" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A36" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A37" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A38" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A39" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A40" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A41" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A42" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A43" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A44" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D44" s="4" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D2" s="1" t="s">
+    <row r="45" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A45" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D45" s="4" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="1" t="s">
+    <row r="46" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A46" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D46" s="4" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
+    <row r="47" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A47" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A48" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A49" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="B49" s="4"/>
+      <c r="C49" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A50" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="D50" s="4" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
+    <row r="51" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A51" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D51" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" s="1" t="s">
+    </row>
+    <row r="52" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A52" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D52" s="4" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="1" t="s">
+    <row r="53" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A53" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D53" s="4" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="1" t="s">
+    <row r="54" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A54" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B54" s="4"/>
+      <c r="C54" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D54" s="4" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D10" s="1" t="s">
+    <row r="55" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A55" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D55" s="4" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D11" s="1" t="s">
+    <row r="56" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A56" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D56" s="4" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>112</v>
-      </c>
-      <c r="C12" t="s">
-        <v>71</v>
-      </c>
-      <c r="D12" t="s">
+    <row r="57" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A57" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B57" s="4"/>
+      <c r="C57" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D57" s="4" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+    <row r="58" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A58" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B58" s="4"/>
+      <c r="C58" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D58" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="C13" t="s">
+    </row>
+    <row r="59" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A59" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B59" s="4"/>
+      <c r="C59" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D59" s="4" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>49</v>
-      </c>
-      <c r="C14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" t="s">
-        <v>73</v>
-      </c>
-      <c r="D15" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>143</v>
-      </c>
-      <c r="C16" t="s">
-        <v>66</v>
-      </c>
-      <c r="D16" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>84</v>
-      </c>
-      <c r="C17" t="s">
-        <v>71</v>
-      </c>
-      <c r="D17" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>68</v>
-      </c>
-      <c r="C18" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>119</v>
-      </c>
-      <c r="C19" t="s">
-        <v>52</v>
-      </c>
-      <c r="D19" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>74</v>
-      </c>
-      <c r="C20" t="s">
-        <v>66</v>
-      </c>
-      <c r="D20" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>57</v>
-      </c>
-      <c r="C21" t="s">
-        <v>58</v>
-      </c>
-      <c r="D21" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>64</v>
-      </c>
-      <c r="C22" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>37</v>
-      </c>
-      <c r="C23" t="s">
-        <v>38</v>
-      </c>
-      <c r="D23" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>152</v>
-      </c>
-      <c r="C24" t="s">
-        <v>52</v>
-      </c>
-      <c r="D24" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" t="s">
-        <v>71</v>
-      </c>
-      <c r="D25" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" t="s">
-        <v>44</v>
-      </c>
-      <c r="D26" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>107</v>
-      </c>
-      <c r="C27" t="s">
-        <v>16</v>
-      </c>
-      <c r="D27" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>86</v>
-      </c>
-      <c r="C28" t="s">
-        <v>34</v>
-      </c>
-      <c r="D28" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>77</v>
-      </c>
-      <c r="C29" t="s">
-        <v>34</v>
-      </c>
-      <c r="D29" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>111</v>
-      </c>
-      <c r="C30" t="s">
-        <v>73</v>
-      </c>
-      <c r="D30" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>62</v>
-      </c>
-      <c r="C31" t="s">
-        <v>60</v>
-      </c>
-      <c r="D31" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>161</v>
-      </c>
-      <c r="C32" t="s">
-        <v>139</v>
-      </c>
-      <c r="D32" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>27</v>
-      </c>
-      <c r="C33" t="s">
-        <v>30</v>
-      </c>
-      <c r="D33" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>164</v>
-      </c>
-      <c r="C34" t="s">
-        <v>12</v>
-      </c>
-      <c r="D34" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>17</v>
-      </c>
-      <c r="C35" t="s">
-        <v>21</v>
-      </c>
-      <c r="D35" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>13</v>
-      </c>
-      <c r="C36" t="s">
-        <v>16</v>
-      </c>
-      <c r="D36" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>90</v>
-      </c>
-      <c r="C37" t="s">
-        <v>16</v>
-      </c>
-      <c r="D37" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>120</v>
-      </c>
-      <c r="C38" t="s">
-        <v>21</v>
-      </c>
-      <c r="D38" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" t="s">
-        <v>118</v>
-      </c>
-      <c r="D39" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>88</v>
-      </c>
-      <c r="C40" t="s">
-        <v>66</v>
-      </c>
-      <c r="D40" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>172</v>
-      </c>
-      <c r="C41" t="s">
-        <v>73</v>
-      </c>
-      <c r="D41" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>96</v>
-      </c>
-      <c r="C42" t="s">
-        <v>97</v>
-      </c>
-      <c r="D42" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>175</v>
-      </c>
-      <c r="C43" t="s">
-        <v>71</v>
-      </c>
-      <c r="D43" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>94</v>
-      </c>
-      <c r="C44" t="s">
-        <v>34</v>
-      </c>
-      <c r="D44" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>100</v>
-      </c>
-      <c r="C45" t="s">
-        <v>66</v>
-      </c>
-      <c r="D45" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>65</v>
-      </c>
-      <c r="C46" t="s">
-        <v>66</v>
-      </c>
-      <c r="D46" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>114</v>
-      </c>
-      <c r="C47" t="s">
-        <v>34</v>
-      </c>
-      <c r="D47" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>46</v>
-      </c>
-      <c r="C48" t="s">
-        <v>12</v>
-      </c>
-      <c r="D48" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>108</v>
-      </c>
-      <c r="C49" t="s">
-        <v>66</v>
-      </c>
-      <c r="D49" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>59</v>
-      </c>
-      <c r="C50" t="s">
-        <v>60</v>
-      </c>
-      <c r="D50" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>105</v>
-      </c>
-      <c r="C51" t="s">
-        <v>55</v>
-      </c>
-      <c r="D51" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>185</v>
-      </c>
-      <c r="C52" t="s">
-        <v>60</v>
-      </c>
-      <c r="D52" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>51</v>
-      </c>
-      <c r="C53" t="s">
-        <v>52</v>
-      </c>
-      <c r="D53" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>87</v>
-      </c>
-      <c r="C54" t="s">
-        <v>12</v>
-      </c>
-      <c r="D54" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>22</v>
-      </c>
-      <c r="C55" t="s">
-        <v>26</v>
-      </c>
-      <c r="D55" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
-        <v>53</v>
-      </c>
-      <c r="C56" t="s">
-        <v>55</v>
-      </c>
-      <c r="D56" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>103</v>
-      </c>
-      <c r="C57" t="s">
-        <v>21</v>
-      </c>
-      <c r="D57" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
-        <v>109</v>
-      </c>
-      <c r="C58" t="s">
-        <v>52</v>
-      </c>
-      <c r="D58" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
-        <v>67</v>
-      </c>
-      <c r="C59" t="s">
-        <v>193</v>
-      </c>
-      <c r="D59" t="s">
-        <v>194</v>
-      </c>
-    </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1754,250 +1828,250 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>195</v>
+        <v>141</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>196</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>197</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>198</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>199</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>200</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>201</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="B7" t="s">
-        <v>202</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="B8" t="s">
-        <v>203</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="B9" t="s">
-        <v>204</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
       <c r="B10" t="s">
-        <v>205</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>117</v>
+        <v>75</v>
       </c>
       <c r="B11" t="s">
-        <v>206</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>207</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B13" t="s">
-        <v>208</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>209</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
-        <v>210</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B16" t="s">
-        <v>211</v>
+        <v>157</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>212</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>213</v>
+        <v>159</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="B19" t="s">
-        <v>214</v>
+        <v>160</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B20" t="s">
-        <v>215</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="B21" t="s">
-        <v>216</v>
+        <v>162</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="B22" t="s">
-        <v>217</v>
+        <v>163</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="B23" t="s">
-        <v>218</v>
+        <v>164</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="B24" t="s">
-        <v>219</v>
+        <v>165</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="B25" t="s">
-        <v>220</v>
+        <v>166</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="B26" t="s">
-        <v>221</v>
+        <v>167</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="B27" t="s">
-        <v>222</v>
+        <v>168</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="B28" t="s">
-        <v>223</v>
+        <v>169</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="B29" t="s">
-        <v>224</v>
+        <v>170</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="B30" t="s">
-        <v>225</v>
+        <v>171</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="B31" t="s">
-        <v>226</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -2010,7 +2084,7 @@
   <dimension ref="A1:G193"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="1" max="1" width="39.90625" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="4" width="10" customWidth="1"/>
     <col min="5" max="6" width="12" customWidth="1"/>
@@ -2041,4419 +2115,4419 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>27</v>
+        <v>208</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>31</v>
+        <v>178</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>31</v>
+        <v>178</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="G8" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>27</v>
+        <v>208</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>190</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>37</v>
+        <v>220</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>27</v>
+        <v>208</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>31</v>
+        <v>178</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>7</v>
+        <v>225</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="G15" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>37</v>
+        <v>220</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>17</v>
+        <v>224</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="F18" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="G18" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>37</v>
+        <v>220</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>31</v>
+        <v>178</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="G21" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>43</v>
+        <v>221</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G23" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>45</v>
+        <v>198</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>46</v>
+        <v>192</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>45</v>
+        <v>198</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="F26" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="G26" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G27" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>27</v>
+        <v>208</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E28" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F28" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="G28" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>46</v>
+        <v>192</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>49</v>
+        <v>180</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>37</v>
+        <v>220</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="F31" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F31" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="G31" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
-        <v>49</v>
+        <v>180</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>46</v>
+        <v>192</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>51</v>
+        <v>194</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>45</v>
+        <v>198</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>53</v>
+        <v>228</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="F36" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F36" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="G36" s="1" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>51</v>
+        <v>194</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
-        <v>45</v>
+        <v>198</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
-        <v>49</v>
+        <v>180</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
-        <v>49</v>
+        <v>180</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="F40" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F40" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="G40" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
-        <v>46</v>
+        <v>192</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
-        <v>51</v>
+        <v>194</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
-        <v>57</v>
+        <v>219</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
-        <v>59</v>
+        <v>193</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="C45" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D45" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="F45" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F45" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="G45" s="1" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
-        <v>57</v>
+        <v>219</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
-        <v>49</v>
+        <v>180</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
-        <v>59</v>
+        <v>193</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
-        <v>57</v>
+        <v>219</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
-        <v>51</v>
+        <v>194</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
-        <v>62</v>
+        <v>206</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D51" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="F51" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F51" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="G51" s="1" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
-        <v>64</v>
+        <v>204</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E52" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G52" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
-        <v>65</v>
+        <v>214</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
-        <v>67</v>
+        <v>222</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
-        <v>68</v>
+        <v>183</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
-        <v>67</v>
+        <v>222</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D56" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="F56" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F56" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="G56" s="1" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
-        <v>68</v>
+        <v>183</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
-        <v>70</v>
+        <v>186</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E58" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F58" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F58" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="G58" s="1" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
-        <v>72</v>
+        <v>181</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
-        <v>62</v>
+        <v>206</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
-        <v>74</v>
+        <v>203</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D61" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E61" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E61" s="1" t="s">
+      <c r="F61" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F61" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="G61" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
-        <v>62</v>
+        <v>206</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
-        <v>76</v>
+        <v>199</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E63" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F63" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F63" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="G63" s="1" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
-        <v>77</v>
+        <v>223</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
-        <v>70</v>
+        <v>186</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
-        <v>78</v>
+        <v>177</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D66" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E66" s="1" t="s">
+      <c r="F66" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F66" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="G66" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
-        <v>77</v>
+        <v>223</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
-        <v>68</v>
+        <v>183</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
-        <v>67</v>
+        <v>222</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
-        <v>76</v>
+        <v>199</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
-        <v>68</v>
+        <v>183</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D71" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E71" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E71" s="1" t="s">
+      <c r="F71" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F71" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="G71" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
-        <v>67</v>
+        <v>222</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
-        <v>70</v>
+        <v>186</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
-        <v>77</v>
+        <v>223</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
-        <v>84</v>
+        <v>182</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D76" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E76" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E76" s="1" t="s">
+      <c r="F76" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F76" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="G76" s="1" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>86</v>
+        <v>187</v>
       </c>
       <c r="B77" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D77" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E77" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F77" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G77" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>87</v>
+        <v>218</v>
       </c>
       <c r="B78" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D78" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E78" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F78" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G78" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>74</v>
+        <v>203</v>
       </c>
       <c r="B79" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D79" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E79" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F79" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G79" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="B80" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D80" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E80" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F80" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G80" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>88</v>
+        <v>209</v>
       </c>
       <c r="B81" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D81" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" t="s">
         <v>9</v>
       </c>
-      <c r="E81" t="s">
+      <c r="F81" t="s">
         <v>10</v>
       </c>
-      <c r="F81" t="s">
-        <v>11</v>
-      </c>
       <c r="G81" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>67</v>
+        <v>222</v>
       </c>
       <c r="B82" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D82" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E82" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F82" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G82" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="B83" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D83" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E83" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F83" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G83" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="B84" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D84" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E84" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F84" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G84" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>86</v>
+        <v>187</v>
       </c>
       <c r="B85" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D85" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E85" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F85" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G85" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>84</v>
+        <v>182</v>
       </c>
       <c r="B86" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D86" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="E86" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F86" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="G86" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="B87" t="s">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D87" t="s">
+        <v>8</v>
+      </c>
+      <c r="E87" t="s">
         <v>9</v>
       </c>
-      <c r="E87" t="s">
+      <c r="F87" t="s">
         <v>10</v>
       </c>
-      <c r="F87" t="s">
-        <v>11</v>
-      </c>
       <c r="G87" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>88</v>
+        <v>209</v>
       </c>
       <c r="B88" t="s">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D88" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E88" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F88" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G88" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>62</v>
+        <v>206</v>
       </c>
       <c r="B89" t="s">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D89" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E89" t="s">
+        <v>17</v>
+      </c>
+      <c r="F89" t="s">
         <v>20</v>
       </c>
-      <c r="F89" t="s">
-        <v>24</v>
-      </c>
       <c r="G89" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>84</v>
+        <v>182</v>
       </c>
       <c r="B90" t="s">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D90" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E90" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F90" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G90" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>86</v>
+        <v>187</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D91" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="E91" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F91" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="G91" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>86</v>
+        <v>187</v>
       </c>
       <c r="B92" t="s">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D92" t="s">
+        <v>8</v>
+      </c>
+      <c r="E92" t="s">
         <v>9</v>
       </c>
-      <c r="E92" t="s">
+      <c r="F92" t="s">
         <v>10</v>
       </c>
-      <c r="F92" t="s">
-        <v>11</v>
-      </c>
       <c r="G92" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>87</v>
+        <v>218</v>
       </c>
       <c r="B93" t="s">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D93" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E93" t="s">
+        <v>10</v>
+      </c>
+      <c r="F93" t="s">
+        <v>13</v>
+      </c>
+      <c r="G93" t="s">
         <v>11</v>
-      </c>
-      <c r="F93" t="s">
-        <v>15</v>
-      </c>
-      <c r="G93" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>84</v>
+        <v>182</v>
       </c>
       <c r="B94" t="s">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D94" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E94" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F94" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G94" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>53</v>
+        <v>228</v>
       </c>
       <c r="B95" t="s">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D95" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E95" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F95" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G95" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>88</v>
+        <v>209</v>
       </c>
       <c r="B96" t="s">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D96" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E96" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F96" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G96" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>43</v>
+        <v>221</v>
       </c>
       <c r="B97" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D97" t="s">
+        <v>8</v>
+      </c>
+      <c r="E97" t="s">
         <v>9</v>
       </c>
-      <c r="E97" t="s">
+      <c r="F97" t="s">
         <v>10</v>
       </c>
-      <c r="F97" t="s">
-        <v>11</v>
-      </c>
       <c r="G97" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="B98" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D98" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E98" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F98" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G98" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>88</v>
+        <v>209</v>
       </c>
       <c r="B99" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D99" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E99" t="s">
+        <v>17</v>
+      </c>
+      <c r="F99" t="s">
         <v>20</v>
       </c>
-      <c r="F99" t="s">
-        <v>24</v>
-      </c>
       <c r="G99" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>87</v>
+        <v>218</v>
       </c>
       <c r="B100" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D100" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E100" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F100" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G100" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>53</v>
+        <v>228</v>
       </c>
       <c r="B101" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D101" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="E101" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F101" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="G101" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>94</v>
+        <v>226</v>
       </c>
       <c r="B102" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D102" t="s">
+        <v>8</v>
+      </c>
+      <c r="E102" t="s">
         <v>9</v>
       </c>
-      <c r="E102" t="s">
+      <c r="F102" t="s">
         <v>10</v>
       </c>
-      <c r="F102" t="s">
-        <v>11</v>
-      </c>
       <c r="G102" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>96</v>
+        <v>211</v>
       </c>
       <c r="B103" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D103" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E103" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F103" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G103" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>72</v>
+        <v>181</v>
       </c>
       <c r="B104" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D104" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E104" t="s">
+        <v>17</v>
+      </c>
+      <c r="F104" t="s">
         <v>20</v>
       </c>
-      <c r="F104" t="s">
-        <v>24</v>
-      </c>
       <c r="G104" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>98</v>
+        <v>176</v>
       </c>
       <c r="B105" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D105" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E105" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F105" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G105" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="B106" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D106" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E106" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F106" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G106" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>100</v>
+        <v>213</v>
       </c>
       <c r="B107" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D107" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E107" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F107" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G107" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>57</v>
+        <v>219</v>
       </c>
       <c r="B108" t="s">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D108" t="s">
+        <v>8</v>
+      </c>
+      <c r="E108" t="s">
         <v>9</v>
       </c>
-      <c r="E108" t="s">
+      <c r="F108" t="s">
         <v>10</v>
       </c>
-      <c r="F108" t="s">
-        <v>11</v>
-      </c>
       <c r="G108" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>100</v>
+        <v>213</v>
       </c>
       <c r="B109" t="s">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D109" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E109" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F109" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G109" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>98</v>
+        <v>176</v>
       </c>
       <c r="B110" t="s">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D110" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E110" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F110" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G110" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>94</v>
+        <v>226</v>
       </c>
       <c r="B111" t="s">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D111" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E111" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F111" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G111" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>72</v>
+        <v>181</v>
       </c>
       <c r="B112" t="s">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D112" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E112" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F112" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G112" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>96</v>
+        <v>211</v>
       </c>
       <c r="B113" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D113" t="s">
+        <v>8</v>
+      </c>
+      <c r="E113" t="s">
         <v>9</v>
       </c>
-      <c r="E113" t="s">
+      <c r="F113" t="s">
         <v>10</v>
       </c>
-      <c r="F113" t="s">
-        <v>11</v>
-      </c>
       <c r="G113" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>94</v>
+        <v>226</v>
       </c>
       <c r="B114" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D114" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E114" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F114" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G114" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>100</v>
+        <v>213</v>
       </c>
       <c r="B115" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D115" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E115" t="s">
+        <v>17</v>
+      </c>
+      <c r="F115" t="s">
         <v>20</v>
       </c>
-      <c r="F115" t="s">
-        <v>24</v>
-      </c>
       <c r="G115" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>76</v>
+        <v>199</v>
       </c>
       <c r="B116" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D116" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E116" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F116" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G116" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>98</v>
+        <v>176</v>
       </c>
       <c r="B117" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D117" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="E117" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F117" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="G117" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>103</v>
+        <v>196</v>
       </c>
       <c r="B118" t="s">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D118" t="s">
+        <v>8</v>
+      </c>
+      <c r="E118" t="s">
         <v>9</v>
       </c>
-      <c r="E118" t="s">
+      <c r="F118" t="s">
         <v>10</v>
       </c>
-      <c r="F118" t="s">
-        <v>11</v>
-      </c>
       <c r="G118" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>105</v>
+        <v>217</v>
       </c>
       <c r="B119" t="s">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D119" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E119" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F119" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G119" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>96</v>
+        <v>211</v>
       </c>
       <c r="B120" t="s">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D120" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E120" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F120" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G120" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="B121" t="s">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D121" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E121" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F121" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G121" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="B122" t="s">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D122" t="s">
+        <v>8</v>
+      </c>
+      <c r="E122" t="s">
         <v>9</v>
       </c>
-      <c r="E122" t="s">
+      <c r="F122" t="s">
         <v>10</v>
       </c>
-      <c r="F122" t="s">
-        <v>11</v>
-      </c>
       <c r="G122" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>107</v>
+        <v>205</v>
       </c>
       <c r="B123" t="s">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D123" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E123" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F123" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G123" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>94</v>
+        <v>226</v>
       </c>
       <c r="B124" t="s">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D124" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E124" t="s">
+        <v>17</v>
+      </c>
+      <c r="F124" t="s">
         <v>20</v>
       </c>
-      <c r="F124" t="s">
-        <v>24</v>
-      </c>
       <c r="G124" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>108</v>
+        <v>216</v>
       </c>
       <c r="B125" t="s">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D125" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E125" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F125" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G125" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>109</v>
+        <v>197</v>
       </c>
       <c r="B126" t="s">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D126" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E126" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F126" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G126" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>108</v>
+        <v>216</v>
       </c>
       <c r="B127" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D127" t="s">
+        <v>8</v>
+      </c>
+      <c r="E127" t="s">
         <v>9</v>
       </c>
-      <c r="E127" t="s">
+      <c r="F127" t="s">
         <v>10</v>
       </c>
-      <c r="F127" t="s">
-        <v>11</v>
-      </c>
       <c r="G127" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>111</v>
+        <v>188</v>
       </c>
       <c r="B128" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D128" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E128" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F128" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G128" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>112</v>
+        <v>202</v>
       </c>
       <c r="B129" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D129" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E129" t="s">
+        <v>17</v>
+      </c>
+      <c r="F129" t="s">
         <v>20</v>
       </c>
-      <c r="F129" t="s">
-        <v>24</v>
-      </c>
       <c r="G129" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>105</v>
+        <v>217</v>
       </c>
       <c r="B130" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D130" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E130" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F130" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G130" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>107</v>
+        <v>205</v>
       </c>
       <c r="B131" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D131" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E131" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F131" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G131" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>111</v>
+        <v>188</v>
       </c>
       <c r="B132" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D132" t="s">
+        <v>8</v>
+      </c>
+      <c r="E132" t="s">
         <v>9</v>
       </c>
-      <c r="E132" t="s">
+      <c r="F132" t="s">
         <v>10</v>
       </c>
-      <c r="F132" t="s">
-        <v>11</v>
-      </c>
       <c r="G132" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>109</v>
+        <v>197</v>
       </c>
       <c r="B133" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D133" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E133" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F133" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G133" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>103</v>
+        <v>196</v>
       </c>
       <c r="B134" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D134" t="s">
+        <v>15</v>
+      </c>
+      <c r="E134" t="s">
+        <v>16</v>
+      </c>
+      <c r="F134" t="s">
+        <v>17</v>
+      </c>
+      <c r="G134" t="s">
         <v>18</v>
-      </c>
-      <c r="E134" t="s">
-        <v>19</v>
-      </c>
-      <c r="F134" t="s">
-        <v>20</v>
-      </c>
-      <c r="G134" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>98</v>
+        <v>176</v>
       </c>
       <c r="B135" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D135" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E135" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F135" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G135" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>114</v>
+        <v>215</v>
       </c>
       <c r="B136" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D136" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E136" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F136" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G136" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>105</v>
+        <v>217</v>
       </c>
       <c r="B137" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D137" t="s">
+        <v>8</v>
+      </c>
+      <c r="E137" t="s">
         <v>9</v>
       </c>
-      <c r="E137" t="s">
+      <c r="F137" t="s">
         <v>10</v>
       </c>
-      <c r="F137" t="s">
-        <v>11</v>
-      </c>
       <c r="G137" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>114</v>
+        <v>215</v>
       </c>
       <c r="B138" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D138" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E138" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F138" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G138" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>111</v>
+        <v>188</v>
       </c>
       <c r="B139" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D139" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E139" t="s">
+        <v>17</v>
+      </c>
+      <c r="F139" t="s">
         <v>20</v>
       </c>
-      <c r="F139" t="s">
-        <v>24</v>
-      </c>
       <c r="G139" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>107</v>
+        <v>205</v>
       </c>
       <c r="B140" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D140" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E140" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F140" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G140" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>108</v>
+        <v>216</v>
       </c>
       <c r="B141" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D141" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E141" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F141" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G141" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>107</v>
+        <v>205</v>
       </c>
       <c r="B142" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D142" t="s">
+        <v>8</v>
+      </c>
+      <c r="E142" t="s">
         <v>9</v>
       </c>
-      <c r="E142" t="s">
+      <c r="F142" t="s">
         <v>10</v>
       </c>
-      <c r="F142" t="s">
-        <v>11</v>
-      </c>
       <c r="G142" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>112</v>
+        <v>202</v>
       </c>
       <c r="B143" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D143" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E143" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F143" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G143" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>43</v>
+        <v>221</v>
       </c>
       <c r="B144" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D144" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E144" t="s">
+        <v>17</v>
+      </c>
+      <c r="F144" t="s">
         <v>20</v>
       </c>
-      <c r="F144" t="s">
-        <v>24</v>
-      </c>
       <c r="G144" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>114</v>
+        <v>215</v>
       </c>
       <c r="B145" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D145" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E145" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F145" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G145" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>111</v>
+        <v>188</v>
       </c>
       <c r="B146" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D146" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E146" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F146" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G146" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>114</v>
+        <v>215</v>
       </c>
       <c r="B147" t="s">
-        <v>117</v>
+        <v>75</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D147" t="s">
+        <v>8</v>
+      </c>
+      <c r="E147" t="s">
         <v>9</v>
       </c>
-      <c r="E147" t="s">
+      <c r="F147" t="s">
         <v>10</v>
       </c>
-      <c r="F147" t="s">
-        <v>11</v>
-      </c>
       <c r="G147" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>105</v>
+        <v>217</v>
       </c>
       <c r="B148" t="s">
-        <v>117</v>
+        <v>75</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D148" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E148" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F148" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G148" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>109</v>
+        <v>197</v>
       </c>
       <c r="B149" t="s">
-        <v>117</v>
+        <v>75</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D149" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E149" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F149" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G149" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>111</v>
+        <v>188</v>
       </c>
       <c r="B150" t="s">
-        <v>117</v>
+        <v>75</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D150" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E150" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F150" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G150" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>112</v>
+        <v>202</v>
       </c>
       <c r="B151" t="s">
-        <v>117</v>
+        <v>75</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D151" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E151" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F151" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G151" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>65</v>
+        <v>214</v>
       </c>
       <c r="B152" t="s">
-        <v>117</v>
+        <v>75</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D152" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E152" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F152" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G152" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>13</v>
+        <v>190</v>
       </c>
       <c r="B153" t="s">
+        <v>7</v>
+      </c>
+      <c r="C153" t="s">
+        <v>174</v>
+      </c>
+      <c r="D153" t="s">
         <v>8</v>
       </c>
-      <c r="C153" t="s">
-        <v>228</v>
-      </c>
-      <c r="D153" t="s">
+      <c r="E153" t="s">
         <v>9</v>
       </c>
-      <c r="E153" t="s">
+      <c r="F153" t="s">
         <v>10</v>
       </c>
-      <c r="F153" t="s">
-        <v>11</v>
-      </c>
       <c r="G153" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
+        <v>225</v>
+      </c>
+      <c r="B154" t="s">
         <v>7</v>
       </c>
-      <c r="B154" t="s">
-        <v>8</v>
-      </c>
       <c r="C154" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D154" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E154" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F154" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G154" t="s">
-        <v>118</v>
+        <v>76</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>119</v>
+        <v>184</v>
       </c>
       <c r="B155" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C155" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D155" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E155" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F155" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G155" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
+        <v>190</v>
+      </c>
+      <c r="B156" t="s">
+        <v>29</v>
+      </c>
+      <c r="C156" t="s">
+        <v>174</v>
+      </c>
+      <c r="D156" t="s">
+        <v>30</v>
+      </c>
+      <c r="E156" t="s">
         <v>13</v>
       </c>
-      <c r="B156" t="s">
-        <v>35</v>
-      </c>
-      <c r="C156" t="s">
-        <v>228</v>
-      </c>
-      <c r="D156" t="s">
-        <v>36</v>
-      </c>
-      <c r="E156" t="s">
-        <v>15</v>
-      </c>
       <c r="F156" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G156" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>7</v>
+        <v>225</v>
       </c>
       <c r="B157" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C157" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D157" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E157" t="s">
+        <v>17</v>
+      </c>
+      <c r="F157" t="s">
         <v>20</v>
       </c>
-      <c r="F157" t="s">
-        <v>24</v>
-      </c>
       <c r="G157" t="s">
-        <v>118</v>
+        <v>76</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>119</v>
+        <v>184</v>
       </c>
       <c r="B158" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C158" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D158" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E158" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F158" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G158" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>7</v>
+        <v>225</v>
       </c>
       <c r="B159" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C159" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D159" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E159" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F159" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G159" t="s">
-        <v>118</v>
+        <v>76</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>13</v>
+        <v>190</v>
       </c>
       <c r="B160" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C160" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D160" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E160" t="s">
+        <v>17</v>
+      </c>
+      <c r="F160" t="s">
         <v>20</v>
       </c>
-      <c r="F160" t="s">
-        <v>24</v>
-      </c>
       <c r="G160" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>119</v>
+        <v>184</v>
       </c>
       <c r="B161" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C161" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D161" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E161" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F161" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G161" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>119</v>
+        <v>184</v>
       </c>
       <c r="B162" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C162" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D162" t="s">
+        <v>8</v>
+      </c>
+      <c r="E162" t="s">
         <v>9</v>
       </c>
-      <c r="E162" t="s">
+      <c r="F162" t="s">
         <v>10</v>
       </c>
-      <c r="F162" t="s">
-        <v>11</v>
-      </c>
       <c r="G162" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>86</v>
+        <v>187</v>
       </c>
       <c r="B163" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C163" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D163" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E163" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F163" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G163" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>59</v>
+        <v>193</v>
       </c>
       <c r="B164" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="C164" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D164" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E164" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F164" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G164" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>51</v>
+        <v>194</v>
       </c>
       <c r="B165" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C165" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D165" t="s">
+        <v>8</v>
+      </c>
+      <c r="E165" t="s">
         <v>9</v>
       </c>
-      <c r="E165" t="s">
+      <c r="F165" t="s">
         <v>10</v>
       </c>
-      <c r="F165" t="s">
-        <v>11</v>
-      </c>
       <c r="G165" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>59</v>
+        <v>193</v>
       </c>
       <c r="B166" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C166" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D166" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E166" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F166" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G166" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>72</v>
+        <v>181</v>
       </c>
       <c r="B167" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C167" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D167" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E167" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F167" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G167" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>68</v>
+        <v>183</v>
       </c>
       <c r="B168" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="C168" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D168" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E168" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F168" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G168" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>78</v>
+        <v>177</v>
       </c>
       <c r="B169" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="C169" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D169" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E169" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F169" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G169" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>68</v>
+        <v>183</v>
       </c>
       <c r="B170" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="C170" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D170" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E170" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F170" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G170" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>68</v>
+        <v>183</v>
       </c>
       <c r="B171" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="C171" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D171" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E171" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F171" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G171" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>86</v>
+        <v>187</v>
       </c>
       <c r="B172" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="C172" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D172" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E172" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F172" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G172" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>86</v>
+        <v>187</v>
       </c>
       <c r="B173" t="s">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="C173" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D173" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E173" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F173" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G173" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>120</v>
+        <v>191</v>
       </c>
       <c r="B174" t="s">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="C174" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D174" t="s">
+        <v>15</v>
+      </c>
+      <c r="E174" t="s">
+        <v>16</v>
+      </c>
+      <c r="F174" t="s">
+        <v>17</v>
+      </c>
+      <c r="G174" t="s">
         <v>18</v>
-      </c>
-      <c r="E174" t="s">
-        <v>19</v>
-      </c>
-      <c r="F174" t="s">
-        <v>20</v>
-      </c>
-      <c r="G174" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>120</v>
+        <v>191</v>
       </c>
       <c r="B175" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="C175" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D175" t="s">
+        <v>8</v>
+      </c>
+      <c r="E175" t="s">
         <v>9</v>
       </c>
-      <c r="E175" t="s">
+      <c r="F175" t="s">
         <v>10</v>
       </c>
-      <c r="F175" t="s">
-        <v>11</v>
-      </c>
       <c r="G175" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>86</v>
+        <v>187</v>
       </c>
       <c r="B176" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="C176" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D176" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E176" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F176" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G176" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>121</v>
+        <v>201</v>
       </c>
       <c r="B177" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="C177" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D177" t="s">
+        <v>8</v>
+      </c>
+      <c r="E177" t="s">
         <v>9</v>
       </c>
-      <c r="E177" t="s">
+      <c r="F177" t="s">
         <v>10</v>
       </c>
-      <c r="F177" t="s">
+      <c r="G177" t="s">
         <v>11</v>
-      </c>
-      <c r="G177" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>72</v>
+        <v>181</v>
       </c>
       <c r="B178" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="C178" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D178" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E178" t="s">
+        <v>17</v>
+      </c>
+      <c r="F178" t="s">
         <v>20</v>
       </c>
-      <c r="F178" t="s">
-        <v>24</v>
-      </c>
       <c r="G178" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>94</v>
+        <v>226</v>
       </c>
       <c r="B179" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="C179" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D179" t="s">
+        <v>23</v>
+      </c>
+      <c r="E179" t="s">
+        <v>21</v>
+      </c>
+      <c r="F179" t="s">
+        <v>24</v>
+      </c>
+      <c r="G179" t="s">
         <v>28</v>
-      </c>
-      <c r="E179" t="s">
-        <v>25</v>
-      </c>
-      <c r="F179" t="s">
-        <v>29</v>
-      </c>
-      <c r="G179" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>94</v>
+        <v>226</v>
       </c>
       <c r="B180" t="s">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="C180" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D180" t="s">
+        <v>8</v>
+      </c>
+      <c r="E180" t="s">
         <v>9</v>
       </c>
-      <c r="E180" t="s">
+      <c r="F180" t="s">
         <v>10</v>
       </c>
-      <c r="F180" t="s">
-        <v>11</v>
-      </c>
       <c r="G180" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>121</v>
+        <v>201</v>
       </c>
       <c r="B181" t="s">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="C181" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D181" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E181" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F181" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G181" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>98</v>
+        <v>176</v>
       </c>
       <c r="B182" t="s">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="C182" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D182" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E182" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F182" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G182" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>72</v>
+        <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="C183" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D183" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="E183" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F183" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="G183" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>72</v>
+        <v>181</v>
       </c>
       <c r="B184" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="C184" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D184" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E184" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F184" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G184" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>121</v>
+        <v>201</v>
       </c>
       <c r="B185" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="C185" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D185" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E185" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F185" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G185" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>94</v>
+        <v>226</v>
       </c>
       <c r="B186" t="s">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="C186" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D186" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E186" t="s">
+        <v>17</v>
+      </c>
+      <c r="F186" t="s">
         <v>20</v>
       </c>
-      <c r="F186" t="s">
-        <v>24</v>
-      </c>
       <c r="G186" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>98</v>
+        <v>176</v>
       </c>
       <c r="B187" t="s">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="C187" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D187" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="E187" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F187" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="G187" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>98</v>
+        <v>176</v>
       </c>
       <c r="B188" t="s">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="C188" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D188" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E188" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F188" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G188" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>111</v>
+        <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="C189" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D189" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E189" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F189" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G189" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>98</v>
+        <v>176</v>
       </c>
       <c r="B190" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="C190" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D190" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E190" t="s">
+        <v>17</v>
+      </c>
+      <c r="F190" t="s">
         <v>20</v>
       </c>
-      <c r="F190" t="s">
-        <v>24</v>
-      </c>
       <c r="G190" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>98</v>
+        <v>176</v>
       </c>
       <c r="B191" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="C191" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D191" t="s">
+        <v>8</v>
+      </c>
+      <c r="E191" t="s">
         <v>9</v>
       </c>
-      <c r="E191" t="s">
+      <c r="F191" t="s">
         <v>10</v>
       </c>
-      <c r="F191" t="s">
-        <v>11</v>
-      </c>
       <c r="G191" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>111</v>
+        <v>188</v>
       </c>
       <c r="B192" t="s">
-        <v>117</v>
+        <v>75</v>
       </c>
       <c r="C192" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D192" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E192" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F192" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G192" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>59</v>
+        <v>193</v>
       </c>
       <c r="B193" t="s">
-        <v>117</v>
+        <v>75</v>
       </c>
       <c r="C193" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="D193" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E193" t="s">
+        <v>17</v>
+      </c>
+      <c r="F193" t="s">
         <v>20</v>
       </c>
-      <c r="F193" t="s">
-        <v>24</v>
-      </c>
       <c r="G193" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
